--- a/artfynd/A 46007-2023 artfynd.xlsx
+++ b/artfynd/A 46007-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121277536</v>
+        <v>121277540</v>
       </c>
       <c r="B2" t="n">
-        <v>56242</v>
+        <v>56266</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205998</v>
+        <v>206002</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -813,10 +813,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121277541</v>
+        <v>121277538</v>
       </c>
       <c r="B3" t="n">
-        <v>56261</v>
+        <v>56259</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -829,26 +829,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -951,10 +951,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121277538</v>
+        <v>121277536</v>
       </c>
       <c r="B4" t="n">
-        <v>56256</v>
+        <v>56245</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -963,30 +963,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>49</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1089,10 +1089,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121277604</v>
+        <v>121277602</v>
       </c>
       <c r="B5" t="n">
-        <v>56261</v>
+        <v>56245</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1101,30 +1101,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1227,10 +1227,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121277602</v>
+        <v>121277604</v>
       </c>
       <c r="B6" t="n">
-        <v>56242</v>
+        <v>56264</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1239,30 +1239,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1365,10 +1365,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121277540</v>
+        <v>121277541</v>
       </c>
       <c r="B7" t="n">
-        <v>56263</v>
+        <v>56264</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1377,25 +1377,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>206002</v>
+        <v>205995</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">

--- a/artfynd/A 46007-2023 artfynd.xlsx
+++ b/artfynd/A 46007-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121277540</v>
+        <v>121277604</v>
       </c>
       <c r="B2" t="n">
-        <v>56266</v>
+        <v>56264</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>206002</v>
+        <v>205995</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549992</v>
+        <v>549999</v>
       </c>
       <c r="R2" t="n">
-        <v>6322756</v>
+        <v>6322765</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -766,7 +766,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -813,10 +813,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121277538</v>
+        <v>121277536</v>
       </c>
       <c r="B3" t="n">
-        <v>56259</v>
+        <v>56245</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -825,30 +825,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>49</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -951,10 +951,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121277536</v>
+        <v>121277541</v>
       </c>
       <c r="B4" t="n">
-        <v>56245</v>
+        <v>56264</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -963,30 +963,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1227,10 +1227,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121277604</v>
+        <v>121277538</v>
       </c>
       <c r="B6" t="n">
-        <v>56264</v>
+        <v>56259</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1243,26 +1243,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1288,10 +1288,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>549999</v>
+        <v>549992</v>
       </c>
       <c r="R6" t="n">
-        <v>6322765</v>
+        <v>6322756</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-08-25</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1365,10 +1365,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121277541</v>
+        <v>121277540</v>
       </c>
       <c r="B7" t="n">
-        <v>56264</v>
+        <v>56266</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1377,25 +1377,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>205995</v>
+        <v>206002</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">

--- a/artfynd/A 46007-2023 artfynd.xlsx
+++ b/artfynd/A 46007-2023 artfynd.xlsx
@@ -813,10 +813,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121277536</v>
+        <v>121277538</v>
       </c>
       <c r="B3" t="n">
-        <v>56245</v>
+        <v>56259</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -825,30 +825,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1089,10 +1089,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121277602</v>
+        <v>121277540</v>
       </c>
       <c r="B5" t="n">
-        <v>56245</v>
+        <v>56266</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1105,26 +1105,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>205998</v>
+        <v>206002</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>549999</v>
+        <v>549992</v>
       </c>
       <c r="R5" t="n">
-        <v>6322765</v>
+        <v>6322756</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1180,7 +1180,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-08-25</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1227,10 +1227,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121277538</v>
+        <v>121277602</v>
       </c>
       <c r="B6" t="n">
-        <v>56259</v>
+        <v>56245</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1239,30 +1239,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1288,10 +1288,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>549992</v>
+        <v>549999</v>
       </c>
       <c r="R6" t="n">
-        <v>6322756</v>
+        <v>6322765</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1365,10 +1365,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121277540</v>
+        <v>121277536</v>
       </c>
       <c r="B7" t="n">
-        <v>56266</v>
+        <v>56245</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1381,26 +1381,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>206002</v>
+        <v>205998</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>49</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">

--- a/artfynd/A 46007-2023 artfynd.xlsx
+++ b/artfynd/A 46007-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121277604</v>
+        <v>121277536</v>
       </c>
       <c r="B2" t="n">
-        <v>56264</v>
+        <v>56245</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>49</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549999</v>
+        <v>549992</v>
       </c>
       <c r="R2" t="n">
-        <v>6322765</v>
+        <v>6322756</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -766,7 +766,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-08-25</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -813,10 +813,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121277538</v>
+        <v>121277604</v>
       </c>
       <c r="B3" t="n">
-        <v>56259</v>
+        <v>56264</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -829,26 +829,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -874,10 +874,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549992</v>
+        <v>549999</v>
       </c>
       <c r="R3" t="n">
-        <v>6322756</v>
+        <v>6322765</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -904,7 +904,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -951,10 +951,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121277541</v>
+        <v>121277538</v>
       </c>
       <c r="B4" t="n">
-        <v>56264</v>
+        <v>56259</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -967,26 +967,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1089,10 +1089,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121277540</v>
+        <v>121277541</v>
       </c>
       <c r="B5" t="n">
-        <v>56266</v>
+        <v>56264</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1101,25 +1101,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>206002</v>
+        <v>205995</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1365,10 +1365,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121277536</v>
+        <v>121277540</v>
       </c>
       <c r="B7" t="n">
-        <v>56245</v>
+        <v>56266</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1381,26 +1381,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>205998</v>
+        <v>206002</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">

--- a/artfynd/A 46007-2023 artfynd.xlsx
+++ b/artfynd/A 46007-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121277536</v>
+        <v>121277604</v>
       </c>
       <c r="B2" t="n">
-        <v>56245</v>
+        <v>56267</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549992</v>
+        <v>549999</v>
       </c>
       <c r="R2" t="n">
-        <v>6322756</v>
+        <v>6322765</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -766,7 +766,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -813,10 +813,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121277604</v>
+        <v>121277538</v>
       </c>
       <c r="B3" t="n">
-        <v>56264</v>
+        <v>56262</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -829,26 +829,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -874,10 +874,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549999</v>
+        <v>549992</v>
       </c>
       <c r="R3" t="n">
-        <v>6322765</v>
+        <v>6322756</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -904,7 +904,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-08-25</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -951,10 +951,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121277538</v>
+        <v>121277540</v>
       </c>
       <c r="B4" t="n">
-        <v>56259</v>
+        <v>56269</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -963,30 +963,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100092</v>
+        <v>206002</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1089,10 +1089,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121277541</v>
+        <v>121277602</v>
       </c>
       <c r="B5" t="n">
-        <v>56264</v>
+        <v>56248</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1101,30 +1101,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>549992</v>
+        <v>549999</v>
       </c>
       <c r="R5" t="n">
-        <v>6322756</v>
+        <v>6322765</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1180,7 +1180,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1227,10 +1227,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121277602</v>
+        <v>121277536</v>
       </c>
       <c r="B6" t="n">
-        <v>56245</v>
+        <v>56248</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>49</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1288,10 +1288,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>549999</v>
+        <v>549992</v>
       </c>
       <c r="R6" t="n">
-        <v>6322765</v>
+        <v>6322756</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-08-25</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1365,10 +1365,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121277540</v>
+        <v>121277541</v>
       </c>
       <c r="B7" t="n">
-        <v>56266</v>
+        <v>56267</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1377,25 +1377,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>206002</v>
+        <v>205995</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">

--- a/artfynd/A 46007-2023 artfynd.xlsx
+++ b/artfynd/A 46007-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121277604</v>
+        <v>121277536</v>
       </c>
       <c r="B2" t="n">
-        <v>56267</v>
+        <v>56248</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>49</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549999</v>
+        <v>549992</v>
       </c>
       <c r="R2" t="n">
-        <v>6322765</v>
+        <v>6322756</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -766,7 +766,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-08-25</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -813,10 +813,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121277538</v>
+        <v>121277602</v>
       </c>
       <c r="B3" t="n">
-        <v>56262</v>
+        <v>56248</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -825,30 +825,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -874,10 +874,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549992</v>
+        <v>549999</v>
       </c>
       <c r="R3" t="n">
-        <v>6322756</v>
+        <v>6322765</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -904,7 +904,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -951,10 +951,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121277540</v>
+        <v>121277538</v>
       </c>
       <c r="B4" t="n">
-        <v>56269</v>
+        <v>56262</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -963,30 +963,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>206002</v>
+        <v>100092</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1089,10 +1089,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121277602</v>
+        <v>121277541</v>
       </c>
       <c r="B5" t="n">
-        <v>56248</v>
+        <v>56267</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1101,30 +1101,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>549999</v>
+        <v>549992</v>
       </c>
       <c r="R5" t="n">
-        <v>6322765</v>
+        <v>6322756</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1180,7 +1180,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-08-25</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1227,10 +1227,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121277536</v>
+        <v>121277540</v>
       </c>
       <c r="B6" t="n">
-        <v>56248</v>
+        <v>56269</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1243,26 +1243,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>205998</v>
+        <v>206002</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1365,7 +1365,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121277541</v>
+        <v>121277604</v>
       </c>
       <c r="B7" t="n">
         <v>56267</v>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1426,10 +1426,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>549992</v>
+        <v>549999</v>
       </c>
       <c r="R7" t="n">
-        <v>6322756</v>
+        <v>6322765</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">

--- a/artfynd/A 46007-2023 artfynd.xlsx
+++ b/artfynd/A 46007-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121277536</v>
+        <v>121277540</v>
       </c>
       <c r="B2" t="n">
-        <v>56248</v>
+        <v>56270</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205998</v>
+        <v>206002</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -813,10 +813,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121277602</v>
+        <v>121277536</v>
       </c>
       <c r="B3" t="n">
-        <v>56248</v>
+        <v>56249</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>49</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -874,10 +874,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549999</v>
+        <v>549992</v>
       </c>
       <c r="R3" t="n">
-        <v>6322765</v>
+        <v>6322756</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -904,7 +904,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-08-25</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -951,10 +951,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121277538</v>
+        <v>121277602</v>
       </c>
       <c r="B4" t="n">
-        <v>56262</v>
+        <v>56249</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -963,30 +963,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1012,10 +1012,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>549992</v>
+        <v>549999</v>
       </c>
       <c r="R4" t="n">
-        <v>6322756</v>
+        <v>6322765</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1089,10 +1089,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121277541</v>
+        <v>121277604</v>
       </c>
       <c r="B5" t="n">
-        <v>56267</v>
+        <v>56268</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>549992</v>
+        <v>549999</v>
       </c>
       <c r="R5" t="n">
-        <v>6322756</v>
+        <v>6322765</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1180,7 +1180,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1227,10 +1227,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121277540</v>
+        <v>121277538</v>
       </c>
       <c r="B6" t="n">
-        <v>56269</v>
+        <v>56263</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1239,30 +1239,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>206002</v>
+        <v>100092</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1365,10 +1365,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121277604</v>
+        <v>121277541</v>
       </c>
       <c r="B7" t="n">
-        <v>56267</v>
+        <v>56268</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1426,10 +1426,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>549999</v>
+        <v>549992</v>
       </c>
       <c r="R7" t="n">
-        <v>6322765</v>
+        <v>6322756</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-08-25</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">

--- a/artfynd/A 46007-2023 artfynd.xlsx
+++ b/artfynd/A 46007-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121277540</v>
+        <v>121277538</v>
       </c>
       <c r="B2" t="n">
-        <v>56270</v>
+        <v>56264</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>206002</v>
+        <v>100092</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -813,10 +813,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121277536</v>
+        <v>121277604</v>
       </c>
       <c r="B3" t="n">
-        <v>56249</v>
+        <v>56269</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -825,30 +825,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -874,10 +874,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549992</v>
+        <v>549999</v>
       </c>
       <c r="R3" t="n">
-        <v>6322756</v>
+        <v>6322765</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -904,7 +904,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -951,10 +951,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121277602</v>
+        <v>121277540</v>
       </c>
       <c r="B4" t="n">
-        <v>56249</v>
+        <v>56271</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -967,26 +967,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205998</v>
+        <v>206002</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1012,10 +1012,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>549999</v>
+        <v>549992</v>
       </c>
       <c r="R4" t="n">
-        <v>6322765</v>
+        <v>6322756</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-08-25</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1089,10 +1089,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121277604</v>
+        <v>121277541</v>
       </c>
       <c r="B5" t="n">
-        <v>56268</v>
+        <v>56269</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>549999</v>
+        <v>549992</v>
       </c>
       <c r="R5" t="n">
-        <v>6322765</v>
+        <v>6322756</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1180,7 +1180,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-08-25</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1227,10 +1227,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121277538</v>
+        <v>121277602</v>
       </c>
       <c r="B6" t="n">
-        <v>56263</v>
+        <v>56250</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1239,30 +1239,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1288,10 +1288,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>549992</v>
+        <v>549999</v>
       </c>
       <c r="R6" t="n">
-        <v>6322756</v>
+        <v>6322765</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1365,10 +1365,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121277541</v>
+        <v>121277536</v>
       </c>
       <c r="B7" t="n">
-        <v>56268</v>
+        <v>56250</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1377,30 +1377,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>49</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">

--- a/artfynd/A 46007-2023 artfynd.xlsx
+++ b/artfynd/A 46007-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121277538</v>
+        <v>121277604</v>
       </c>
       <c r="B2" t="n">
-        <v>56264</v>
+        <v>56269</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549992</v>
+        <v>549999</v>
       </c>
       <c r="R2" t="n">
-        <v>6322756</v>
+        <v>6322765</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -766,7 +766,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -813,10 +813,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121277604</v>
+        <v>121277540</v>
       </c>
       <c r="B3" t="n">
-        <v>56269</v>
+        <v>56271</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -825,30 +825,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205995</v>
+        <v>206002</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -874,10 +874,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549999</v>
+        <v>549992</v>
       </c>
       <c r="R3" t="n">
-        <v>6322765</v>
+        <v>6322756</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -904,7 +904,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-08-25</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -951,10 +951,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121277540</v>
+        <v>121277602</v>
       </c>
       <c r="B4" t="n">
-        <v>56271</v>
+        <v>56250</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -967,26 +967,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>206002</v>
+        <v>205998</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1012,10 +1012,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>549992</v>
+        <v>549999</v>
       </c>
       <c r="R4" t="n">
-        <v>6322756</v>
+        <v>6322765</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1227,7 +1227,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121277602</v>
+        <v>121277536</v>
       </c>
       <c r="B6" t="n">
         <v>56250</v>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>49</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1288,10 +1288,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>549999</v>
+        <v>549992</v>
       </c>
       <c r="R6" t="n">
-        <v>6322765</v>
+        <v>6322756</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-08-25</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1365,10 +1365,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121277536</v>
+        <v>121277538</v>
       </c>
       <c r="B7" t="n">
-        <v>56250</v>
+        <v>56264</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1377,30 +1377,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">

--- a/artfynd/A 46007-2023 artfynd.xlsx
+++ b/artfynd/A 46007-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121277604</v>
+        <v>121277538</v>
       </c>
       <c r="B2" t="n">
-        <v>56269</v>
+        <v>56264</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549999</v>
+        <v>549992</v>
       </c>
       <c r="R2" t="n">
-        <v>6322765</v>
+        <v>6322756</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -766,7 +766,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-08-25</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -813,10 +813,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121277540</v>
+        <v>121277604</v>
       </c>
       <c r="B3" t="n">
-        <v>56271</v>
+        <v>56269</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -825,30 +825,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>206002</v>
+        <v>205995</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -874,10 +874,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549992</v>
+        <v>549999</v>
       </c>
       <c r="R3" t="n">
-        <v>6322756</v>
+        <v>6322765</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -904,7 +904,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1227,10 +1227,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121277536</v>
+        <v>121277540</v>
       </c>
       <c r="B6" t="n">
-        <v>56250</v>
+        <v>56271</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1243,26 +1243,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>205998</v>
+        <v>206002</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1365,10 +1365,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121277538</v>
+        <v>121277536</v>
       </c>
       <c r="B7" t="n">
-        <v>56264</v>
+        <v>56250</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1377,30 +1377,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>49</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">

--- a/artfynd/A 46007-2023 artfynd.xlsx
+++ b/artfynd/A 46007-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121277538</v>
+        <v>121277536</v>
       </c>
       <c r="B2" t="n">
-        <v>56264</v>
+        <v>56250</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>49</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -813,10 +813,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121277604</v>
+        <v>121277538</v>
       </c>
       <c r="B3" t="n">
-        <v>56269</v>
+        <v>56264</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -829,26 +829,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -874,10 +874,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549999</v>
+        <v>549992</v>
       </c>
       <c r="R3" t="n">
-        <v>6322765</v>
+        <v>6322756</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -904,7 +904,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-08-25</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -951,10 +951,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121277602</v>
+        <v>121277604</v>
       </c>
       <c r="B4" t="n">
-        <v>56250</v>
+        <v>56269</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -963,30 +963,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1089,10 +1089,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121277541</v>
+        <v>121277540</v>
       </c>
       <c r="B5" t="n">
-        <v>56269</v>
+        <v>56271</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1101,25 +1101,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>205995</v>
+        <v>206002</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1227,10 +1227,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121277540</v>
+        <v>121277602</v>
       </c>
       <c r="B6" t="n">
-        <v>56271</v>
+        <v>56250</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1243,26 +1243,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>206002</v>
+        <v>205998</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1288,10 +1288,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>549992</v>
+        <v>549999</v>
       </c>
       <c r="R6" t="n">
-        <v>6322756</v>
+        <v>6322765</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1365,10 +1365,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121277536</v>
+        <v>121277541</v>
       </c>
       <c r="B7" t="n">
-        <v>56250</v>
+        <v>56269</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1377,30 +1377,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">

--- a/artfynd/A 46007-2023 artfynd.xlsx
+++ b/artfynd/A 46007-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121277604</v>
+        <v>121277538</v>
       </c>
       <c r="B2" t="n">
-        <v>56270</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56830</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,26 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -736,10 +731,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549999</v>
+        <v>549992</v>
       </c>
       <c r="R2" t="n">
-        <v>6322765</v>
+        <v>6322756</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -766,7 +761,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -776,7 +771,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-08-25</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -816,12 +811,7 @@
         <v>121277541</v>
       </c>
       <c r="B3" t="n">
-        <v>56270</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56835</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -951,42 +941,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121277602</v>
+        <v>121277604</v>
       </c>
       <c r="B4" t="n">
-        <v>56251</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56835</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1089,42 +1074,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121277538</v>
+        <v>121277536</v>
       </c>
       <c r="B5" t="n">
-        <v>56265</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56816</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>49</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1227,15 +1207,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121277536</v>
+        <v>121277602</v>
       </c>
       <c r="B6" t="n">
-        <v>56251</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56816</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1262,7 +1237,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1288,10 +1263,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>549992</v>
+        <v>549999</v>
       </c>
       <c r="R6" t="n">
-        <v>6322756</v>
+        <v>6322765</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1318,7 +1293,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1328,7 +1303,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1368,12 +1343,7 @@
         <v>121277540</v>
       </c>
       <c r="B7" t="n">
-        <v>56272</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56837</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 46007-2023 artfynd.xlsx
+++ b/artfynd/A 46007-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -805,6 +810,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121277538</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -938,6 +948,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121277541</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1071,6 +1086,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121277604</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1204,6 +1224,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121277536</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1337,6 +1362,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121277602</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1470,8 +1500,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121277540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>